--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18168.78</v>
+        <v>17933.94</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2269.45</v>
+        <v>2240.11</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1239.93</v>
+        <v>1223.9</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2446.6</v>
+        <v>2414.98</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1730.48</v>
+        <v>1708.11</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8862.91</v>
+        <v>8748.35</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2469.08</v>
+        <v>2437.17</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3450.54</v>
+        <v>3405.94</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11643.93</v>
+        <v>11493.42</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7953.12</v>
+        <v>7850.33</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5883.17</v>
+        <v>5807.12</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3053.18</v>
+        <v>3013.72</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6773.23</v>
+        <v>6685.68</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3292.68</v>
+        <v>3250.12</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5280.41</v>
+        <v>5212.15</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2164.6</v>
+        <v>2136.62</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4526.07</v>
+        <v>4467.56</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>943.3200000000001</v>
+        <v>931.13</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2596.6</v>
+        <v>2563.04</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1071.59</v>
+        <v>1057.74</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5166.72</v>
+        <v>5099.94</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4004.36</v>
+        <v>3952.6</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>35809.21</v>
+        <v>35346.35</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4475.34</v>
+        <v>4417.49</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4084.77</v>
+        <v>4031.97</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4365.75</v>
+        <v>4309.32</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11025.15</v>
+        <v>10882.65</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5456.45</v>
+        <v>5385.93</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>784.53</v>
+        <v>774.39</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4550.38</v>
+        <v>4491.57</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1832.96</v>
+        <v>1809.27</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3685.29</v>
+        <v>3637.65</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5790.92</v>
+        <v>5716.07</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2294.84</v>
+        <v>2265.17</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10895.32</v>
+        <v>10754.5</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>26809.42</v>
+        <v>26468.88</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9183.52</v>
+        <v>9066.870000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5992.03</v>
+        <v>5915.91</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2281.21</v>
+        <v>2252.24</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2192.58</v>
+        <v>2164.73</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2443.83</v>
+        <v>2412.78</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2944.81</v>
+        <v>2907.4</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>37111.26</v>
+        <v>36639.87</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5082.84</v>
+        <v>5018.27</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12622.15</v>
+        <v>12461.82</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>810.16</v>
+        <v>799.87</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1091.03</v>
+        <v>1077.17</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4436.04</v>
+        <v>4379.69</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1887.39</v>
+        <v>1863.41</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>12513.89</v>
+        <v>12354.94</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3265.42</v>
+        <v>3223.95</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>18802.76</v>
+        <v>18563.92</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6768.28</v>
+        <v>6682.31</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6102.37</v>
+        <v>6024.85</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5298.49</v>
+        <v>5231.19</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2228.19</v>
+        <v>2199.88</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>9116.950000000001</v>
+        <v>9001.139999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>873.1799999999999</v>
+        <v>862.09</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3086.18</v>
+        <v>3046.97</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5144.52</v>
+        <v>5079.18</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>20399.15</v>
+        <v>20140.04</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5870.06</v>
+        <v>5795.49</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3524.81</v>
+        <v>3480.04</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8867.709999999999</v>
+        <v>8755.07</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5390.42</v>
+        <v>5321.95</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>6006.3</v>
+        <v>5930.01</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>12069.83</v>
+        <v>11916.52</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>923.28</v>
+        <v>911.55</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>12718.75</v>
+        <v>12557.19</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2470.22</v>
+        <v>2438.84</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4366.88</v>
+        <v>4311.41</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1402.24</v>
+        <v>1384.42</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>75652.22</v>
+        <v>74691.27</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5577.23</v>
+        <v>5506.39</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5952.24</v>
+        <v>5876.63</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7734.66</v>
+        <v>7636.42</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2830.23</v>
+        <v>2802.07</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5450.06</v>
+        <v>5395.83</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1480.11</v>
+        <v>1465.39</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>20743.08</v>
+        <v>20536.69</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>14653.65</v>
+        <v>14507.85</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12157.08</v>
+        <v>12036.12</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>17582.6</v>
+        <v>17407.66</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2226.27</v>
+        <v>2204.12</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>876.7</v>
+        <v>867.97</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>9480.85</v>
+        <v>9386.52</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3482.76</v>
+        <v>3448.11</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3015.96</v>
+        <v>2985.95</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2821.38</v>
+        <v>2793.3</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7528.27</v>
+        <v>7453.37</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3434.63</v>
+        <v>3400.45</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7090.83</v>
+        <v>7020.28</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3446.15</v>
+        <v>3411.86</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1427.48</v>
+        <v>1413.27</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2195.39</v>
+        <v>2173.55</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7422.25</v>
+        <v>7348.4</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>764.62</v>
+        <v>757.02</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2277.43</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4003.74</v>
+        <v>3963.91</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6395.27</v>
+        <v>6331.64</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5086.73</v>
+        <v>5036.12</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2516.02</v>
+        <v>2490.99</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2535.6</v>
+        <v>2510.37</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>19707.49</v>
+        <v>19511.41</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>12570.84</v>
+        <v>12445.77</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>4920.96</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2671.54</v>
+        <v>2644.96</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>11134.39</v>
+        <v>11023.61</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5668.13</v>
+        <v>5611.73</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3323.51</v>
+        <v>3290.45</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>22454.01</v>
+        <v>22230.6</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2728.72</v>
+        <v>2701.57</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>14377.81</v>
+        <v>14234.76</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5154.95</v>
+        <v>5103.66</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2662.09</v>
+        <v>2635.6</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8310.42</v>
+        <v>8227.74</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1075.49</v>
+        <v>1064.78</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1580.7</v>
+        <v>1564.97</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1076.42</v>
+        <v>1065.71</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2794.05</v>
+        <v>2766.25</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>52496.16</v>
+        <v>51973.85</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>10593.19</v>
+        <v>10487.8</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>830.58</v>
+        <v>822.3099999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>32728.91</v>
+        <v>32403.27</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2464.14</v>
+        <v>2439.62</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2992.01</v>
+        <v>2962.24</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3024.77</v>
+        <v>2994.67</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3426.23</v>
+        <v>3392.14</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10637.95</v>
+        <v>10599.81</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>810.3099999999999</v>
+        <v>807.41</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3806.08</v>
+        <v>3792.43</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2369.77</v>
+        <v>2361.27</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3612.78</v>
+        <v>3599.82</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4349.66</v>
+        <v>4334.07</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2279.68</v>
+        <v>2271.5</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2899.58</v>
+        <v>2889.19</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>12479.81</v>
+        <v>12435.06</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>4244.17</v>
+        <v>4228.95</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4276.81</v>
+        <v>4261.48</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1832</v>
+        <v>1825.43</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1162.97</v>
+        <v>1158.8</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5400.09</v>
+        <v>5380.73</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>16070.84</v>
+        <v>16013.22</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>16905.26</v>
+        <v>16844.64</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>38700.06</v>
+        <v>38561.29</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4858.73</v>
+        <v>4841.3</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3293.04</v>
+        <v>3281.23</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>10422.39</v>
+        <v>10385.02</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>836.64</v>
+        <v>833.64</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>778.54</v>
+        <v>775.75</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2796.28</v>
+        <v>2786.25</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11573.16</v>
+        <v>11531.66</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2814.21</v>
+        <v>2804.12</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2320.01</v>
+        <v>2311.69</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2711.38</v>
+        <v>2701.66</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4457.71</v>
+        <v>4441.72</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>962.5599999999999</v>
+        <v>959.11</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1583.77</v>
+        <v>1578.09</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4534.05</v>
+        <v>4517.8</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2756.38</v>
+        <v>2746.49</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>8569.33</v>
+        <v>8538.610000000001</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8509.389999999999</v>
+        <v>8478.879999999999</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2352.25</v>
+        <v>2343.82</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>6226.28</v>
+        <v>6203.96</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>15967.45</v>
+        <v>15910.2</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2966.68</v>
+        <v>2956.04</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5873.09</v>
+        <v>5852.03</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10623.47</v>
+        <v>10585.38</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1967.28</v>
+        <v>1960.23</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3183.52</v>
+        <v>3172.1</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1294.92</v>
+        <v>1290.28</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3971.89</v>
+        <v>3957.64</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1584.06</v>
+        <v>1578.38</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>761.2</v>
+        <v>758.48</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>901.55</v>
+        <v>899.59</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2421.81</v>
+        <v>2416.57</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1705.19</v>
+        <v>1701.5</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3261.58</v>
+        <v>3254.52</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>843.36</v>
+        <v>841.53</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>28236.83</v>
+        <v>28175.72</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>6634.33</v>
+        <v>6619.97</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>7449.78</v>
+        <v>7433.66</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3899.18</v>
+        <v>3890.74</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2498.45</v>
+        <v>2493.04</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3873.11</v>
+        <v>3864.73</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>11322.59</v>
+        <v>11298.08</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3367.91</v>
+        <v>3360.62</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2814.45</v>
+        <v>2808.36</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3235.87</v>
+        <v>3228.87</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4024.93</v>
+        <v>4016.22</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2086.46</v>
+        <v>2081.94</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>7159.51</v>
+        <v>7144.02</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2484.76</v>
+        <v>2479.38</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>32124.28</v>
+        <v>32054.76</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1194.05</v>
+        <v>1191.46</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>870.21</v>
+        <v>868.3200000000001</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2418.21</v>
+        <v>2412.97</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6062.14</v>
+        <v>6049.02</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1250.84</v>
+        <v>1248.13</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2359.35</v>
+        <v>2354.25</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2024.75</v>
+        <v>2020.37</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2838.35</v>
+        <v>2832.2</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>7855.72</v>
+        <v>7838.72</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1056.13</v>
+        <v>1053.85</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2547.89</v>
+        <v>2537.21</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1115.7</v>
+        <v>1111.02</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3219.08</v>
+        <v>3205.58</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2938.49</v>
+        <v>2926.17</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3397.04</v>
+        <v>3382.8</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>761.41</v>
+        <v>758.22</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2496.09</v>
+        <v>2485.63</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2537.99</v>
+        <v>2527.35</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3970.65</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>783.88</v>
+        <v>780.6</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>5624.24</v>
+        <v>5600.66</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4742.57</v>
+        <v>4722.69</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4098.42</v>
+        <v>4081.24</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2291.91</v>
+        <v>2282.31</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>6360.34</v>
+        <v>6333.68</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2281.32</v>
+        <v>2271.75</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1669.15</v>
+        <v>1662.15</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3190.39</v>
+        <v>3177.02</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3341.12</v>
+        <v>3327.11</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1947.3</v>
+        <v>1939.14</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>6582.52</v>
+        <v>6554.93</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>838.4299999999999</v>
+        <v>834.92</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>24791.89</v>
+        <v>24687.95</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>43243.48</v>
+        <v>43062.19</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>34353.68</v>
+        <v>34209.66</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>5977.52</v>
+        <v>5952.46</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2602.71</v>
+        <v>2591.8</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1889.11</v>
+        <v>1881.19</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>5425.06</v>
+        <v>5402.32</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4768.25</v>
+        <v>4748.26</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1239.93</v>
+        <v>1234.73</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1039.55</v>
+        <v>1035.19</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3168.62</v>
+        <v>3155.34</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4593.67</v>
+        <v>4574.42</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>7889.65</v>
+        <v>7856.57</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>15969.26</v>
+        <v>15902.31</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3579.74</v>
+        <v>3564.74</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3505.15</v>
+        <v>3490.45</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3942.59</v>
+        <v>3926.06</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>6577.66</v>
+        <v>6550.09</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5335.45</v>
+        <v>5313.08</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>7916.59</v>
+        <v>7883.4</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>892.8099999999999</v>
+        <v>882.48</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3241.48</v>
+        <v>3203.97</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4593.86</v>
+        <v>4540.7</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>14734.15</v>
+        <v>14563.63</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>9358.15</v>
+        <v>9249.84</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3279.77</v>
+        <v>3241.82</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>5525.1</v>
+        <v>5461.16</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2928.37</v>
+        <v>2894.48</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1248.55</v>
+        <v>1234.1</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4702.95</v>
+        <v>4648.52</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1385.16</v>
+        <v>1369.13</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4170.48</v>
+        <v>4122.22</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1089.92</v>
+        <v>1077.31</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3722.11</v>
+        <v>3679.03</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>20506.74</v>
+        <v>20269.41</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4060.02</v>
+        <v>4013.04</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>18780.09</v>
+        <v>18562.75</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5659.04</v>
+        <v>5593.55</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2593.37</v>
+        <v>2563.36</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>10446.24</v>
+        <v>10325.34</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2052.31</v>
+        <v>2028.56</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5646.27</v>
+        <v>5580.92</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2347.84</v>
+        <v>2320.67</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>9032.59</v>
+        <v>8928.059999999999</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>10838.8</v>
+        <v>10713.36</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2760.33</v>
+        <v>2728.39</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3959.42</v>
+        <v>3913.6</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1356.88</v>
+        <v>1341.17</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2180.07</v>
+        <v>2154.84</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2369.19</v>
+        <v>2341.77</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1669.61</v>
+        <v>1650.29</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7177.44</v>
+        <v>7094.37</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>4457.25</v>
+        <v>4405.66</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>6194.9</v>
+        <v>6123.21</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4588.74</v>
+        <v>4535.63</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>843.63</v>
+        <v>833.87</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>7023.47</v>
+        <v>6942.18</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>10823.22</v>
+        <v>10697.96</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>807.89</v>
+        <v>801.04</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4146.81</v>
+        <v>4111.68</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3069.07</v>
+        <v>3043.08</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2570.35</v>
+        <v>2548.57</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>810.1900000000001</v>
+        <v>803.3200000000001</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>7586.85</v>
+        <v>7522.58</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2284.16</v>
+        <v>2264.81</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1091.39</v>
+        <v>1082.14</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>7696.27</v>
+        <v>7631.07</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>10120.44</v>
+        <v>10034.71</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2454.91</v>
+        <v>2434.12</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>4336.62</v>
+        <v>4299.89</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>5279.57</v>
+        <v>5234.84</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>4366.02</v>
+        <v>4329.03</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2388.67</v>
+        <v>2368.43</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>35459.85</v>
+        <v>35159.47</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1727.76</v>
+        <v>1713.13</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2183.24</v>
+        <v>2164.75</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2465.43</v>
+        <v>2444.55</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3548.07</v>
+        <v>3518.01</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2805.75</v>
+        <v>2781.98</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>8059.65</v>
+        <v>7991.37</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>45377.28</v>
+        <v>44992.89</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2439.85</v>
+        <v>2419.18</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>6858.17</v>
+        <v>6800.07</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>7731.97</v>
+        <v>7666.48</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>778.75</v>
+        <v>772.16</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2566.44</v>
+        <v>2544.7</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>6349.2</v>
+        <v>6295.41</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>811.3200000000001</v>
+        <v>804.45</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>14409.32</v>
+        <v>14287.26</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3185.65</v>
+        <v>3158.66</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>14818.32</v>
+        <v>14692.8</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2668.35</v>
+        <v>2645.75</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>807.63</v>
+        <v>800.79</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>8226.23</v>
+        <v>8156.55</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2103.69</v>
+        <v>2085.87</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3699.25</v>
+        <v>3667.92</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>25248.09</v>
+        <v>25034.22</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>3400.51</v>
+        <v>3371.7</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>967.34</v>
+        <v>959.15</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>2768.83</v>
+        <v>2745.37</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>4362.07</v>
+        <v>4358.56</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>7394.32</v>
+        <v>7388.37</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2346.84</v>
+        <v>2344.95</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2471.76</v>
+        <v>2469.77</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>3768.88</v>
+        <v>3765.85</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>6793.35</v>
+        <v>6787.89</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1469.04</v>
+        <v>1467.86</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>8353.639999999999</v>
+        <v>8346.92</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>7639.69</v>
+        <v>7633.55</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>4236.02</v>
+        <v>4232.61</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>5681.59</v>
+        <v>5677.02</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>3329.2</v>
+        <v>3326.52</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3468.7</v>
+        <v>3465.91</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2049.95</v>
+        <v>2048.3</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>3426.18</v>
+        <v>3423.43</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2376.76</v>
+        <v>2374.85</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>23362.91</v>
+        <v>23344.13</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>4230.34</v>
+        <v>4226.94</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>883.83</v>
+        <v>883.12</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>4984.72</v>
+        <v>4980.71</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>3932.26</v>
+        <v>3929.1</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>6026.16</v>
+        <v>6021.32</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1217.29</v>
+        <v>1216.31</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>2653.34</v>
+        <v>2651.2</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>6220.58</v>
+        <v>6215.58</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>7634.64</v>
+        <v>7628.5</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>15539.81</v>
+        <v>15527.32</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2289.55</v>
+        <v>2287.71</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1140.71</v>
+        <v>1139.79</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6456.81</v>
+        <v>6451.62</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>8429.139999999999</v>
+        <v>8422.370000000001</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2858.71</v>
+        <v>2856.42</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1515.56</v>
+        <v>1514.34</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3556.02</v>
+        <v>3553.16</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1488.9</v>
+        <v>1487.7</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>25098.69</v>
+        <v>25078.51</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2394.59</v>
+        <v>2392.67</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1701.34</v>
+        <v>1699.97</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2303.53</v>
+        <v>2301.67</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>5303.6</v>
+        <v>5299.34</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1397.31</v>
+        <v>1396.19</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>7747.58</v>
+        <v>7741.36</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3273.29</v>
+        <v>3270.66</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>11808.26</v>
+        <v>11798.77</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1718.07</v>
+        <v>1716.69</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2538.04</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2689.61</v>
+        <v>2687.45</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>4820.96</v>
+        <v>4839.47</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>5869.45</v>
+        <v>5891.98</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>5965.08</v>
+        <v>5987.98</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>205880.78</v>
+        <v>206670.99</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>53186.47</v>
+        <v>53390.61</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1689.93</v>
+        <v>1696.42</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2279.95</v>
+        <v>2288.7</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1186.54</v>
+        <v>1191.1</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>6612.51</v>
+        <v>6637.89</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2284.71</v>
+        <v>2293.47</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2442.11</v>
+        <v>2451.48</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>14735.76</v>
+        <v>14792.32</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1158.72</v>
+        <v>1163.17</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1186.8</v>
+        <v>1191.35</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>5801.83</v>
+        <v>5824.1</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2954.01</v>
+        <v>2965.35</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2925.6</v>
+        <v>2936.83</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>2989.93</v>
+        <v>3001.4</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1913.86</v>
+        <v>1921.2</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2836.48</v>
+        <v>2847.36</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>822.79</v>
+        <v>825.9400000000001</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2550.98</v>
+        <v>2560.77</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1955.78</v>
+        <v>1963.29</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>47828.19</v>
+        <v>48011.77</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1818.38</v>
+        <v>1825.36</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>4767.86</v>
+        <v>4786.16</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>2387.15</v>
+        <v>2397.97</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>11642.65</v>
+        <v>11695.41</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1272.92</v>
+        <v>1278.69</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>5390.06</v>
+        <v>5414.48</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>759.85</v>
+        <v>763.3</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1382.82</v>
+        <v>1389.09</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>5478.23</v>
+        <v>5503.05</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>957.49</v>
+        <v>961.83</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>2869.44</v>
+        <v>2882.45</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2380.42</v>
+        <v>2391.21</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>4471.21</v>
+        <v>4491.48</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>3878.47</v>
+        <v>3896.05</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>8458.42</v>
+        <v>8496.75</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1600.4</v>
+        <v>1607.65</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>13465.73</v>
+        <v>13526.75</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>829.99</v>
+        <v>833.76</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>4138.87</v>
+        <v>4157.62</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1195.92</v>
+        <v>1201.33</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>6920</v>
+        <v>6951.36</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3218.77</v>
+        <v>3233.35</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>3879.13</v>
+        <v>3896.71</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>6395.63</v>
+        <v>6424.61</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>21754.07</v>
+        <v>21852.65</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>9832.639999999999</v>
+        <v>9877.200000000001</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>8257.139999999999</v>
+        <v>8294.559999999999</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>3883.94</v>
+        <v>3901.55</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>13384.3</v>
+        <v>13444.96</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>764.92</v>
+        <v>768.39</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>2389.71</v>
+        <v>2400.54</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>26026.64</v>
+        <v>26144.58</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1111.85</v>
+        <v>1116.89</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2675.44</v>
+        <v>2687.57</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>10910.76</v>
+        <v>10960.2</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>3798.6</v>
+        <v>3815.82</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>1116.79</v>
+        <v>1121.85</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>2000.31</v>
+        <v>2009.37</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>3274.93</v>
+        <v>3289.77</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>14620.37</v>
+        <v>14686.62</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>6900.06</v>
+        <v>6931.33</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>3857.35</v>
+        <v>3874.83</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>42841.86</v>
+        <v>43036</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2837.69</v>
+        <v>2845.21</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>7056.01</v>
+        <v>7074.72</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1669.89</v>
+        <v>1674.32</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>11301.47</v>
+        <v>11331.44</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>4184.24</v>
+        <v>4195.33</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>963.61</v>
+        <v>966.16</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>2293.97</v>
+        <v>2300.06</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>1866.67</v>
+        <v>1871.62</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>22915.7</v>
+        <v>22976.46</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>6034.93</v>
+        <v>6050.93</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2429.7</v>
+        <v>2436.14</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2849.45</v>
+        <v>2857.01</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2013.52</v>
+        <v>2018.86</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>6157.74</v>
+        <v>6174.07</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>23079.13</v>
+        <v>23140.33</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>7691.92</v>
+        <v>7712.32</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>6310.09</v>
+        <v>6326.82</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>5554.99</v>
+        <v>5569.72</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>4981.13</v>
+        <v>4994.34</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>4087.31</v>
+        <v>4098.15</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2182.76</v>
+        <v>2188.55</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>834.2</v>
+        <v>836.41</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>19873.1</v>
+        <v>19925.8</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3622.38</v>
+        <v>3631.99</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>6722.42</v>
+        <v>6740.25</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>7374.09</v>
+        <v>7393.64</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>1786.72</v>
+        <v>1791.46</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>768.47</v>
+        <v>770.5</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2987.15</v>
+        <v>2995.07</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>6183.5</v>
+        <v>6199.9</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>2411.53</v>
+        <v>2417.92</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>2462.71</v>
+        <v>2469.24</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1745.72</v>
+        <v>1750.34</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1693.44</v>
+        <v>1697.93</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>5413.8</v>
+        <v>5428.15</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>4370.13</v>
+        <v>4381.72</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>3058.64</v>
+        <v>3066.75</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4511.91</v>
+        <v>4523.87</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>6400.01</v>
+        <v>6416.98</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1388.38</v>
+        <v>1392.06</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>4653.55</v>
+        <v>4665.89</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>1568.87</v>
+        <v>1566.67</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>2167.66</v>
+        <v>2164.62</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>2114.6</v>
+        <v>2111.64</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>2389.28</v>
+        <v>2385.93</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>1222.48</v>
+        <v>1220.77</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>20788.12</v>
+        <v>20758.96</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>4802.42</v>
+        <v>4795.68</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>10809.95</v>
+        <v>10794.79</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2680.21</v>
+        <v>2676.45</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2292.63</v>
+        <v>2289.42</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>22731.92</v>
+        <v>22700.03</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>12698.89</v>
+        <v>12681.07</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>942.63</v>
+        <v>941.3099999999999</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>2677.6</v>
+        <v>2673.85</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>11094.02</v>
+        <v>11078.46</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>3044.71</v>
+        <v>3040.44</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2034.28</v>
+        <v>2031.42</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>3594.69</v>
+        <v>3589.65</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>6246.13</v>
+        <v>6237.37</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2681.79</v>
+        <v>2678.03</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1393.57</v>
+        <v>1391.62</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>8798.85</v>
+        <v>8786.5</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>6869.21</v>
+        <v>6859.57</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>1505.68</v>
+        <v>1503.57</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2453.82</v>
+        <v>2450.38</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1751.52</v>
+        <v>1749.06</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>20399.15</v>
+        <v>20370.54</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2788.16</v>
+        <v>2784.25</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>3370.89</v>
+        <v>3366.16</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>1074.19</v>
+        <v>1072.68</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>21670.59</v>
+        <v>21640.19</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3570.88</v>
+        <v>3565.87</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>8645.77</v>
+        <v>8633.639999999999</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>7162.79</v>
+        <v>7152.74</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2864.06</v>
+        <v>2860.05</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>12558.94</v>
+        <v>12541.32</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1471.85</v>
+        <v>1469.79</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>760.1</v>
+        <v>759.03</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>1884.16</v>
+        <v>1881.52</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>5237.15</v>
+        <v>5229.8</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2511.02</v>
+        <v>2507.5</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1881.56</v>
+        <v>1878.92</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>19534.09</v>
+        <v>19506.69</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>82811.61</v>
+        <v>82695.44</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2619.06</v>
+        <v>2622.41</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>20136.13</v>
+        <v>20161.94</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1486.01</v>
+        <v>1487.92</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>42634.61</v>
+        <v>42689.27</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1401.5</v>
+        <v>1403.3</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2414.36</v>
+        <v>2417.46</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1302.3</v>
+        <v>1303.97</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>6205.02</v>
+        <v>6212.97</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1711.93</v>
+        <v>1714.12</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>4522.38</v>
+        <v>4528.18</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>1252.8</v>
+        <v>1254.41</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>2203.38</v>
+        <v>2206.2</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>7793.37</v>
+        <v>7803.36</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2142.57</v>
+        <v>2145.31</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2287.87</v>
+        <v>2290.81</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>920.26</v>
+        <v>921.4400000000001</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1315.84</v>
+        <v>1317.53</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>5184.45</v>
+        <v>5191.09</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>5179.71</v>
+        <v>5186.35</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>865.65</v>
+        <v>866.76</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2358.49</v>
+        <v>2361.51</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>3086.18</v>
+        <v>3090.13</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>899.77</v>
+        <v>900.92</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>4890.15</v>
+        <v>4896.42</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2961.48</v>
+        <v>2965.28</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>4863.76</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>10848.64</v>
+        <v>10862.54</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>4786.95</v>
+        <v>4793.09</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>6965.37</v>
+        <v>6974.3</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2712.55</v>
+        <v>2716.03</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>4714.34</v>
+        <v>4720.38</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>10079.17</v>
+        <v>10092.09</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>6323.15</v>
+        <v>6366.68</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>14758.7</v>
+        <v>14860.29</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>884.95</v>
+        <v>891.04</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>5672.01</v>
+        <v>5711.05</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>2646.25</v>
+        <v>2664.47</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>5690.6</v>
+        <v>5729.77</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>3357.51</v>
+        <v>3380.63</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2511.45</v>
+        <v>2528.74</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>1324.48</v>
+        <v>1333.6</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>8928.110000000001</v>
+        <v>8989.57</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1948.34</v>
+        <v>1961.75</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1340.01</v>
+        <v>1349.23</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>6574.81</v>
+        <v>6620.07</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2882.4</v>
+        <v>2902.24</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>4046.62</v>
+        <v>4074.47</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2286.77</v>
+        <v>2302.51</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1908.86</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>843.4400000000001</v>
+        <v>849.24</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>5655.01</v>
+        <v>5693.94</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>3273.22</v>
+        <v>3295.75</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1545.59</v>
+        <v>1556.23</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>5723.45</v>
+        <v>5762.85</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2362.69</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>8550.58</v>
+        <v>8609.43</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2084.92</v>
+        <v>2102.74</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>1079.38</v>
+        <v>1088.61</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1784.88</v>
+        <v>1800.14</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>4171.13</v>
+        <v>4206.78</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>14877.28</v>
+        <v>15004.42</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2698.4</v>
+        <v>2721.46</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>10165.68</v>
+        <v>10252.55</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1347.47</v>
+        <v>1358.99</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>2183.67</v>
+        <v>2202.33</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>2183.67</v>
+        <v>2202.33</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2183.67</v>
+        <v>2202.33</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>3723.15</v>
+        <v>3754.97</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2729.11</v>
+        <v>2752.43</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1237.07</v>
+        <v>1247.64</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>2643.86</v>
+        <v>2666.45</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1022.36</v>
+        <v>1031.1</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>816.1</v>
+        <v>823.0700000000001</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>6226.56</v>
+        <v>6279.77</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2183.67</v>
+        <v>2202.33</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>4494.95</v>
+        <v>4533.36</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>3170.73</v>
+        <v>3197.82</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>2779.11</v>
+        <v>2802.86</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>1748.6</v>
+        <v>1763.54</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>2161.22</v>
+        <v>2179.69</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>4676.02</v>
+        <v>4715.98</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>6146.76</v>
+        <v>6199.29</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>1558.67</v>
+        <v>1571.99</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>5240.28</v>
+        <v>5285.07</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2636.06</v>
+        <v>2658.58</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>3809.1</v>
+        <v>3841.65</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>4602.69</v>
+        <v>4642.03</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>10110.31</v>
+        <v>10196.71</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>20426.64</v>
+        <v>20601.2</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>17741.16</v>
+        <v>17892.77</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>7459.29</v>
+        <v>7523.04</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>3370.36</v>
+        <v>3399.16</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>15002.24</v>
+        <v>15130.45</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>947.67</v>
+        <v>955.77</v>
       </c>
     </row>
     <row r="621">
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>6548.36</v>
+        <v>6618.6</v>
       </c>
     </row>
     <row r="622">
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3677.5</v>
+        <v>3716.94</v>
       </c>
     </row>
     <row r="623">
@@ -38450,7 +38450,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>11065.89</v>
+        <v>11184.59</v>
       </c>
     </row>
     <row r="624">
@@ -38511,7 +38511,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1864.56</v>
+        <v>1884.56</v>
       </c>
     </row>
     <row r="625">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>7869.62</v>
+        <v>7954.04</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>48237.9</v>
+        <v>48755.33</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>6733.86</v>
+        <v>6806.1</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>7876.89</v>
+        <v>7961.38</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2278.13</v>
+        <v>2302.57</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1274.68</v>
+        <v>1288.35</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>3192.17</v>
+        <v>3226.41</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>26734.15</v>
+        <v>27020.92</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>15510.89</v>
+        <v>15677.27</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2367.52</v>
+        <v>2392.92</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>3804.72</v>
+        <v>3845.54</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>3623.92</v>
+        <v>3662.79</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>5242.06</v>
+        <v>5298.29</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>11742.94</v>
+        <v>11868.9</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>2618.32</v>
+        <v>2646.4</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>2117.72</v>
+        <v>2140.44</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>4337.08</v>
+        <v>4383.6</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>4416.18</v>
+        <v>4463.55</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3793</v>
+        <v>3833.69</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>16452.2</v>
+        <v>16628.68</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>54574.72</v>
+        <v>55160.12</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>1850.24</v>
+        <v>1870.09</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>9353.52</v>
+        <v>9453.85</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>2536.38</v>
+        <v>2563.59</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>3220.71</v>
+        <v>3255.25</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>2098.96</v>
+        <v>2121.47</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>2180.24</v>
+        <v>2203.62</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>6774.25</v>
+        <v>6846.91</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>53059</v>
+        <v>53628.14</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>3720.77</v>
+        <v>3766.5</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>4508.47</v>
+        <v>4563.88</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1332.32</v>
+        <v>1348.7</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>20431.15</v>
+        <v>20682.25</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>1600.37</v>
+        <v>1620.04</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>2280.16</v>
+        <v>2308.18</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>24868.91</v>
+        <v>25174.55</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>2590.05</v>
+        <v>2621.89</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>2924.57</v>
+        <v>2960.51</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>10441.04</v>
+        <v>10569.36</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>1554.43</v>
+        <v>1573.53</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>18116.62</v>
+        <v>18339.28</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>7600.95</v>
+        <v>7694.37</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>3534.39</v>
+        <v>3577.82</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>9313.08</v>
+        <v>9427.540000000001</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>11526.4</v>
+        <v>11668.06</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2280.6</v>
+        <v>2309.91</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>1693.03</v>
+        <v>1714.78</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>23813.06</v>
+        <v>24119.05</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>768.62</v>
+        <v>778.5</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>2961.27</v>
+        <v>2999.33</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>10491.44</v>
+        <v>10626.25</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2210.26</v>
+        <v>2238.66</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>2290.46</v>
+        <v>2319.89</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>2281.81</v>
+        <v>2311.13</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>14563.54</v>
+        <v>14750.68</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>7500.34</v>
+        <v>7596.72</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>9219.040000000001</v>
+        <v>9337.5</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>4940.22</v>
+        <v>5003.7</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1521.68</v>
+        <v>1541.24</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>2613.05</v>
+        <v>2646.63</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>3111.18</v>
+        <v>3151.15</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>6421.08</v>
+        <v>6503.59</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>2095.71</v>
+        <v>2122.64</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>16483.75</v>
+        <v>16695.56</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>2589.35</v>
+        <v>2622.62</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>2976.03</v>
+        <v>3014.27</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>15850.85</v>
+        <v>16054.53</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>6525.65</v>
+        <v>6609.5</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>4538.86</v>
+        <v>4597.18</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2291.85</v>
+        <v>2321.3</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>4091.26</v>
+        <v>4143.83</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>3247.24</v>
+        <v>3288.96</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>21721.77</v>
+        <v>22000.88</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>11130.7</v>
+        <v>11273.73</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>5926.07</v>
+        <v>6002.22</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>3620.76</v>
+        <v>3667.29</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>5419.05</v>
+        <v>5448.69</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>1500.88</v>
+        <v>1509.09</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>1365.4</v>
+        <v>1372.87</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>8208.309999999999</v>
+        <v>8253.200000000001</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2467.3</v>
+        <v>2480.8</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2313.9</v>
+        <v>2326.56</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>12766.63</v>
+        <v>12836.44</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>2508.66</v>
+        <v>2522.38</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3920.93</v>
+        <v>3942.37</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1926.12</v>
+        <v>1936.65</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>45338.73</v>
+        <v>45586.67</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>2008.74</v>
+        <v>2019.73</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1727.79</v>
+        <v>1737.24</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2510.36</v>
+        <v>2524.09</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>5775.63</v>
+        <v>5807.22</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>1440.84</v>
+        <v>1448.72</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>1053.73</v>
+        <v>1059.49</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>8328.92</v>
+        <v>8374.469999999999</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>5436.42</v>
+        <v>5466.15</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>26513.05</v>
+        <v>26658.05</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>3663.36</v>
+        <v>3683.4</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>6188.72</v>
+        <v>6222.56</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>5300.08</v>
+        <v>5329.06</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>3639.51</v>
+        <v>3659.41</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>4465.6</v>
+        <v>4490.02</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>19912.07</v>
+        <v>20020.96</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>6329.78</v>
+        <v>6364.39</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>3845.72</v>
+        <v>3866.75</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2286.8</v>
+        <v>2299.3</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>1969.31</v>
+        <v>1980.08</v>
       </c>
     </row>
     <row r="731">
@@ -45046,7 +45046,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>17348.28</v>
+        <v>17443.16</v>
       </c>
     </row>
     <row r="732">
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>10261.27</v>
+        <v>10317.39</v>
       </c>
     </row>
     <row r="733">
@@ -45168,7 +45168,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>2184</v>
+        <v>2195.94</v>
       </c>
     </row>
     <row r="734">
@@ -45229,7 +45229,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>10597.72</v>
+        <v>10655.67</v>
       </c>
     </row>
     <row r="735">
@@ -45290,7 +45290,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>3930.9</v>
+        <v>3952.4</v>
       </c>
     </row>
     <row r="736">
@@ -45351,7 +45351,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>4093.18</v>
+        <v>4115.57</v>
       </c>
     </row>
     <row r="737">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>2391.95</v>
+        <v>2405.03</v>
       </c>
     </row>
     <row r="738">
@@ -45473,7 +45473,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>860.39</v>
+        <v>865.09</v>
       </c>
     </row>
     <row r="739">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>4810.59</v>
+        <v>4836.9</v>
       </c>
     </row>
     <row r="740">
@@ -45595,7 +45595,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>9573.25</v>
+        <v>9625.6</v>
       </c>
     </row>
     <row r="741">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>2271.24</v>
+        <v>2283.66</v>
       </c>
     </row>
     <row r="742">
@@ -45717,7 +45717,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>2557.96</v>
+        <v>2571.95</v>
       </c>
     </row>
     <row r="743">
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>6083.51</v>
+        <v>6116.78</v>
       </c>
     </row>
     <row r="744">
@@ -45839,7 +45839,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>3659.75</v>
+        <v>3679.76</v>
       </c>
     </row>
     <row r="745">
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>17932.03</v>
+        <v>18030.09</v>
       </c>
     </row>
     <row r="746">
@@ -45961,7 +45961,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>5181.29</v>
+        <v>5209.63</v>
       </c>
     </row>
     <row r="747">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>28179.23</v>
+        <v>28333.33</v>
       </c>
     </row>
     <row r="748">
@@ -46083,7 +46083,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>9182.42</v>
+        <v>9232.639999999999</v>
       </c>
     </row>
     <row r="749">
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>1417.23</v>
+        <v>1424.98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41667,7 +41667,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42704,7 +42704,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43802,7 +43802,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
@@ -44721,7 +44721,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -45087,7 +45087,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45148,7 +45148,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45331,7 +45331,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO CONTROL FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Femenino Semiabierto St</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>IMPO PAPER SPA</t>
+          <t>Impo Paper Spa</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Said Mauricio Tarzijan Julian</t>
+          <t>SAID MAURICIO TARZIJAN JULIAN</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Museo Marítimo Nacional</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Economato CPF San Miguel</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIO</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15733,12 +15733,12 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16038,12 +16038,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18793,7 +18793,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -19210,12 +19210,12 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>IIIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Servicio Agricola y Ganadero</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24405,7 +24405,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -24944,7 +24944,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Escuadrilla de Abastecimiento del Edificio FF.AA.</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -24954,7 +24954,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25625,7 +25625,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -26784,7 +26784,7 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -27750,7 +27750,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28665,7 +28665,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30129,7 +30129,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
@@ -30495,7 +30495,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -30749,7 +30749,7 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -30861,7 +30861,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -31105,7 +31105,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31532,7 +31532,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31837,7 +31837,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>INSTITUTO GEOGRAFICO MILITAR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -31847,7 +31847,7 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32203,7 +32203,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -32630,7 +32630,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32691,7 +32691,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>SERPLAC III Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
@@ -33057,7 +33057,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33179,7 +33179,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33189,7 +33189,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>BASTIAN IGNACIO</t>
+          <t>Bastian Ignacio</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -33911,7 +33911,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34043,7 +34043,7 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34165,7 +34165,7 @@
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>INGESCOM LTDA.</t>
+          <t>Ingescom ltda.</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Secretaría Ministerial de Educación - RM</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34531,7 +34531,7 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
@@ -34653,7 +34653,7 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -35019,7 +35019,7 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -35385,7 +35385,7 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
@@ -35629,7 +35629,7 @@
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
@@ -35751,7 +35751,7 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
@@ -35863,7 +35863,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -35924,7 +35924,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -35985,7 +35985,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -36168,7 +36168,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36178,7 +36178,7 @@
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J586" t="inlineStr">
@@ -36778,7 +36778,7 @@
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -37337,7 +37337,7 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
@@ -37449,7 +37449,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -37571,7 +37571,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -37815,7 +37815,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38120,7 +38120,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38171,7 +38171,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
@@ -38181,7 +38181,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Neurocirugía</t>
+          <t>Instituto de Neurocirugía</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -38547,7 +38547,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Dirección General de Gendarmería de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38795,7 +38795,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Museo Marítimo Nacional</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -38856,7 +38856,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -38988,7 +38988,7 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39161,7 +39161,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39456,7 +39456,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -39537,7 +39537,7 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
@@ -39781,7 +39781,7 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
@@ -40203,7 +40203,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40320,7 +40320,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40513,7 +40513,7 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
@@ -40686,7 +40686,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41062,7 +41062,7 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
@@ -41235,7 +41235,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -41245,7 +41245,7 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
@@ -41479,7 +41479,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -41662,7 +41662,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -42150,7 +42150,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -42516,7 +42516,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -42760,7 +42760,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -42943,7 +42943,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -43309,7 +43309,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -44112,7 +44112,7 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -45143,7 +45143,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45692,7 +45692,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -45875,7 +45875,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -46007,7 +46007,7 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
@@ -46119,7 +46119,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
@@ -623,7 +623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2480,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2931,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3057,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3309,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3374,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3439,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3504,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3695,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3821,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3886,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4142,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4333,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4398,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4524,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4589,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4654,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4719,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4845,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5093,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5219,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5284,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5540,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5666,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5796,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5861,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5926,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5991,11 @@
           <t>77.879.842-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6056,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6121,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6186,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6434,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6499,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6625,11 @@
           <t>77.879.842-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6751,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6816,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6881,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7007,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7259,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7446,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7511,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7576,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7702,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7767,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7832,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8267,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8332,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8397,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8523,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8653,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8718,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8844,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8909,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8974,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9039,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9165,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9291,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9356,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9421,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9551,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9616,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9746,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9811,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9937,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10002,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10067,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10132,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10197,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10262,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10327,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10644,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10709,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10896,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11274,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11400,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11465,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11595,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11660,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11786,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11851,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11977,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12103,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12229,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12294,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12359,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12485,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12550,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12676,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13050,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13115,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13241,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13306,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13432,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13497,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13749,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13879,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14009,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14444,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14509,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14574,11 @@
           <t>77.916.035-1</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14700,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14765,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14830,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14956,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15147,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15212,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15277,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15342,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15407,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15472,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15598,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15724,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15915,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16236,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16301,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16366,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16431,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16557,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16622,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16992,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17057,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17122,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17187,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17508,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18016,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18081,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18207,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18333,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18459,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18524,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18589,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18654,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18780,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19154,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19280,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19345,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19410,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19536,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19784,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20101,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20227,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20719,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20845,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21158,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21288,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21479,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21731,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21796,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22117,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22308,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22438,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22568,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22633,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22698,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22763,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22828,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22893,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23088,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23458,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23523,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23653,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23718,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23783,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23909,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24096,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24283,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24348,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24474,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24539,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24604,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24795,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24860,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24986,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25051,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25238,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25303,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25490,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25555,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25620,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25685,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25750,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25815,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25941,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26067,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26132,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26197,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26262,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26388,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26579,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26644,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26770,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26896,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27022,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27209,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27400,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27526,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27656,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27851,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27977,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28042,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28172,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28237,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28302,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28432,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28688,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28814,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28879,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29009,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29074,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29139,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29204,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29269,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29590,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29655,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29785,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29911,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29976,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30106,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30301,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30366,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30553,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30618,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30683,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30748,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30935,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31000,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31065,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31191,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31321,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31512,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31703,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31768,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31833,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31898,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32024,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32150,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32215,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32341,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32406,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32471,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32536,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32601,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32788,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32853,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +32918,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32983,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33170,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33235,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33544,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33609,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33674,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33739,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33926,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +33991,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34117,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34182,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34247,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34312,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34503,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34568,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34694,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34759,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34824,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +34954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35145,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35210,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35275,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35340,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35466,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35531,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35787,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35917,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +35982,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36108,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36173,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36238,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36303,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36555,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36620,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36685,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36811,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +36998,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37128,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37437,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +37502,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37567,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37632,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37697,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37823,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +37888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37953,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +38018,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38083,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38148,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38278,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +38408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38473,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38603,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38729,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38794,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38859,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38924,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39050,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39115,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39180,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39306,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39371,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39436,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39501,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39566,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +39696,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39826,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +39952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +40082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +40147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +40277,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40407,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40472,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40659,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +40785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +40911,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +40976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41102,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41167,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +41232,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +41484,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +41671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +41736,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +41862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +41988,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42053,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42118,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +42183,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +42248,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +42374,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +42439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +42504,11 @@
           <t>77.922.408-2</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +42569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +42695,11 @@
           <t>77.045.877-3</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +42760,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +42825,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43012,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +43199,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +43325,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +43390,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +43516,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +43581,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +43646,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +43711,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +43776,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +43841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +43967,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44032,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +44162,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +44227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +44292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +44357,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +44422,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +44487,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +44613,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +44678,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +44743,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +44808,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +44873,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +44938,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45129,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +45194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +45320,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +45385,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +45450,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +45698,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +45824,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +45889,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +45954,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46019,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44246,7 +46210,11 @@
           <t>77.934.122-4</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +46275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +46340,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44612,7 +46588,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +46714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44856,7 +46840,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +46905,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +47031,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +47096,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +47222,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +47535,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +47600,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45649,7 +47665,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45710,7 +47730,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +47795,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45832,7 +47860,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +47925,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +48112,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +48177,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/dic-2025.xlsx
@@ -2996,7 +2996,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5158,7 +5162,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7324,7 +7332,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8206,7 +8218,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10522,7 +10538,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11339,7 +11359,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13371,7 +13395,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17317,7 +17345,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19032,7 +19064,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19849,7 +19885,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20475,7 +20515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21036,7 +21080,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21353,7 +21401,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21544,7 +21596,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21861,7 +21917,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23336,7 +23396,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24222,7 +24286,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +24481,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24925,7 +24997,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25880,7 +25956,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26006,7 +26086,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26709,7 +26793,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27916,7 +28004,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34442,7 +34534,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36937,7 +37033,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37193,7 +37293,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37315,7 +37419,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38989,7 +39097,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40724,7 +40836,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41297,7 +41413,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41549,7 +41669,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41610,7 +41734,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45515,7 +45643,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46084,7 +46216,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48051,7 +48187,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
